--- a/output/pdf_financials_xlsx/FORA.xlsx
+++ b/output/pdf_financials_xlsx/FORA.xlsx
@@ -1429,10 +1429,10 @@
         <v>6.015184</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.189315</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>16.373449</v>
       </c>
     </row>
     <row r="35">
@@ -1479,10 +1479,10 @@
         <v>6.015184</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.189315</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>16.373449</v>
       </c>
     </row>
     <row r="37">
@@ -1779,10 +1779,10 @@
         <v>2.343261</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.15881</v>
+        <v>1.969495</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17.599279</v>
+        <v>1.22583</v>
       </c>
     </row>
     <row r="49">
@@ -3813,13 +3813,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.822191</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.945076</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-1.352625</v>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
@@ -3844,13 +3844,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.822191</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.945076</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-1.352625</v>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9832,7 +9832,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -11014,7 +11018,11 @@
           <t>Lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E151" s="5" t="n">
         <v>-0.822191</v>
       </c>
@@ -12054,7 +12062,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -12918,7 +12926,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">

--- a/output/pdf_financials_xlsx/FORA.xlsx
+++ b/output/pdf_financials_xlsx/FORA.xlsx
@@ -507,15 +507,11 @@
       <c r="D4" s="3" t="n">
         <v>80.488146</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>60.899089</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>69.052081</v>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -538,15 +534,11 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -569,15 +561,11 @@
       <c r="D6" s="3" t="n">
         <v>80.488146</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>60.899089</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>69.052081</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -600,15 +588,11 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -631,15 +615,11 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -662,15 +642,11 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -693,15 +669,11 @@
       <c r="D10" s="3" t="n">
         <v>104.517454</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>63.891852</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>61.729683</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -724,15 +696,11 @@
       <c r="D11" s="3" t="n">
         <v>-24.029308</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-2.992763</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>7.322398</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -755,15 +723,11 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -786,15 +750,11 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
@@ -817,15 +777,11 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
@@ -848,15 +804,11 @@
       <c r="D15" s="3" t="n">
         <v>-0.021753</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>-0.031661</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-0.080376</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -879,15 +831,11 @@
       <c r="D16" s="3" t="n">
         <v>-27.105105</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-7.867948</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1.745009</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -910,15 +858,11 @@
       <c r="D17" s="3" t="n">
         <v>2.333054</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>2.916993</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-1.760872</v>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
@@ -1015,15 +959,11 @@
       <c r="D20" s="3" t="n">
         <v>-24.772051</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-4.950955</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.015863</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1046,15 +986,11 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
@@ -1077,15 +1013,11 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
@@ -1108,20 +1040,14 @@
       <c r="D23" s="3" t="n">
         <v>-24.772051</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>-4.950955</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-0.015863</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-8.02169</v>
       </c>
     </row>
     <row r="24">
@@ -1139,10 +1065,8 @@
       <c r="D24" s="3" t="n">
         <v>-1.16</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.23</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
@@ -1170,10 +1094,8 @@
       <c r="D25" s="3" t="n">
         <v>-1.16</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.23</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
@@ -1201,10 +1123,8 @@
       <c r="D26" s="3" t="n">
         <v>21.355216</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>21.525891</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1232,15 +1152,11 @@
       <c r="D27" s="3" t="n">
         <v>-27.105105</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-7.867948</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1.745009</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1263,15 +1179,11 @@
       <c r="D28" s="3" t="n">
         <v>38.659197</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>21.321892</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>17.892421</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -1294,15 +1206,11 @@
       <c r="D29" s="3" t="n">
         <v>11.554092</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>13.453944</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>19.63743</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1325,15 +1233,11 @@
       <c r="D30" s="3" t="n">
         <v>14.35502316080184</v>
       </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="3" t="n">
+        <v>22.09219254494923</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>28.4385781219251</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1356,15 +1260,11 @@
       <c r="D31" s="3" t="n">
         <v>-8.607433913279436</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-37.07438076611589</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>100.909049752752</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -1387,15 +1287,11 @@
       <c r="D32" s="3" t="n">
         <v>-30.77726625731943</v>
       </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="3" t="n">
+        <v>-8.129768575027452</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-0.02297251548436317</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
@@ -3044,20 +2940,14 @@
       <c r="D99" s="3" t="n">
         <v>-24.772051</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-4.950955</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-0.015863</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-8.02169</v>
       </c>
     </row>
     <row r="100">
@@ -3075,20 +2965,14 @@
       <c r="D100" s="3" t="n">
         <v>38.659197</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>21.321892</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>17.892421</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>21.175916</v>
       </c>
     </row>
     <row r="101">
@@ -3106,20 +2990,14 @@
       <c r="D101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3137,20 +3015,14 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3168,20 +3040,14 @@
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3199,20 +3065,14 @@
       <c r="D104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3230,20 +3090,14 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3261,20 +3115,14 @@
       <c r="D106" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3292,20 +3140,14 @@
       <c r="D107" s="3" t="n">
         <v>9.809234</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>4.517052</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>4.091018</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>2.573905</v>
       </c>
     </row>
     <row r="108">
@@ -3323,20 +3165,14 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3354,20 +3190,14 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3385,20 +3215,14 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3416,20 +3240,14 @@
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3447,20 +3265,14 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3478,20 +3290,14 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3509,20 +3315,14 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3532,7 +3332,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.81925</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -3540,20 +3340,14 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.01711</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3571,20 +3365,14 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3602,20 +3390,14 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3633,20 +3415,14 @@
       <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3666,20 +3442,14 @@
       <c r="D119" s="3" t="n">
         <v>-9.6576</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>-17.066523</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>-2.130361</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>-10.891313</v>
       </c>
     </row>
     <row r="120">
@@ -3697,20 +3467,14 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3728,20 +3492,14 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3759,20 +3517,14 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3790,20 +3542,14 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3821,20 +3567,14 @@
       <c r="D124" s="3" t="n">
         <v>-1.352625</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>-1.455419</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>-1.36337</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>-0.901875</v>
       </c>
     </row>
     <row r="125">
@@ -3852,20 +3592,14 @@
       <c r="D125" s="3" t="n">
         <v>-1.352625</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>-1.455419</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>-1.36337</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>-0.901875</v>
       </c>
     </row>
     <row r="126">
@@ -3883,20 +3617,14 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3951,20 +3679,14 @@
       <c r="D128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3982,20 +3704,14 @@
       <c r="D129" s="3" t="n">
         <v>-22.473868</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>-1.134162</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>-23.377675</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>3.594339</v>
       </c>
     </row>
     <row r="130">
@@ -4013,20 +3729,14 @@
       <c r="D130" s="3" t="n">
         <v>20.494313</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>8.766769</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>6.015184</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>5.189315</v>
       </c>
     </row>
     <row r="131">
@@ -4044,20 +3754,14 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4075,20 +3779,14 @@
       <c r="D132" s="3" t="n">
         <v>-11.495568</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>-2.693934</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.734398</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>11.251386</v>
       </c>
     </row>
     <row r="133">
@@ -4106,20 +3804,14 @@
       <c r="D133" s="3" t="n">
         <v>8.766769</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>6.015184</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>5.189315</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>16.373449</v>
       </c>
     </row>
     <row r="134">
@@ -4137,20 +3829,14 @@
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4170,20 +3856,14 @@
       <c r="D135" s="3" t="n">
         <v>20.6359</v>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>15.506751</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>24.773638</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>18.54836</v>
       </c>
     </row>
   </sheetData>
@@ -4197,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8806,20 +8486,14 @@
       <c r="G102" s="5" t="n">
         <v>-24.772051</v>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>-4.950955</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.015863</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-8.02169</v>
       </c>
     </row>
     <row r="103">
@@ -8835,7 +8509,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 7, 8, and 9)</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8848,26 +8522,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>20.636368</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>38.659197</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="5" t="n">
+        <v>17.892421</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>21.175916</v>
       </c>
     </row>
     <row r="104">
@@ -8883,7 +8557,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net interest expense (note 19)</t>
+          <t>Net interest and financing expense (note 16)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8892,26 +8566,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>6.073298</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>3.094352</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="5" t="n">
+        <v>5.684899</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>3.057518</v>
       </c>
     </row>
     <row r="105">
@@ -8927,7 +8601,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Loss on sale of assets</t>
+          <t>Gain on sale of assets</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8936,26 +8610,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>0.411209</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.003198</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.17845</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>-0.010024</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>-0.136495</v>
       </c>
     </row>
     <row r="106">
@@ -8971,7 +8643,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Loss on sale of investments</t>
+          <t>Gain on sale of investments</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8980,8 +8652,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>0.000402</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -8993,10 +8667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="5" t="n">
+        <v>-0.01711</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -9017,14 +8689,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Unrealized loss in derivative instruments</t>
+          <t>Unrealized loss (gain) in derivative instruments</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="5" t="n">
+        <v>-0.080957</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>0.062181</v>
@@ -9032,20 +8702,14 @@
       <c r="G107" s="5" t="n">
         <v>0.018325</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H107" s="5" t="n">
+        <v>-0.051303</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0.196371</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>-0.155797</v>
       </c>
     </row>
     <row r="108">
@@ -9061,7 +8725,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Loan forgiveness</t>
+          <t>Income tax expense (note 12)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -9070,8 +8734,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.899289</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -9083,15 +8749,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="5" t="n">
+        <v>1.760872</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0.108414</v>
       </c>
     </row>
     <row r="109">
@@ -9107,7 +8769,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Impairment of Investment (note 10)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -9116,11 +8778,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>1</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -9132,10 +8798,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J109" s="5" t="n">
+        <v>-0.101658</v>
       </c>
     </row>
     <row r="110">
@@ -9151,35 +8815,37 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Income tax recovery (note 14)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Share-based compensation (note 11)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>-1.830045</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>-2.333054</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>4.517052</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>4.091018</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>2.573905</v>
       </c>
     </row>
     <row r="111">
@@ -9195,35 +8861,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Adjustment to contingent considerations (note 4)</t>
+          <t>Items not involving cash total</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="5" t="n">
+        <v>25.432128</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>1.71</v>
+        <v>20.282249</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2.671222</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.150423</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>21.777108</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>29.582584</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>18.500113</v>
       </c>
     </row>
     <row r="112">
@@ -9239,39 +8897,33 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 13)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Change in non-cash operating assets and liabilities (note 13)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>6.132391</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>9.809234</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>-1.068235</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>-0.317</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>2.923445</v>
       </c>
     </row>
     <row r="113">
@@ -9287,33 +8939,37 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Items not involving cash total</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>25.432128</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>20.282249</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>28.150423</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest paid (note 9)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>-4.507773</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>-4.121413</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>-2.897295</v>
       </c>
     </row>
     <row r="114">
@@ -9329,7 +8985,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Change in non-cash operating assets and liabilities (note 15)</t>
+          <t>Income taxes refunded (paid)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -9338,26 +8994,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>1.564976</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>-1.346439</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="5" t="n">
+        <v>-0.370533</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.022097</v>
       </c>
     </row>
     <row r="115">
@@ -9373,37 +9029,39 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Net cash provided by operating activities</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>-6.629541</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>-2.005649</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>-2.307714</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="5" t="n">
+        <v>24.773638</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>18.54836</v>
       </c>
     </row>
     <row r="116">
@@ -9414,37 +9072,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Income taxes paid</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>-0.39184</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-0.238942</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>-3.86037</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repayment of term loan</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>-43.75</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -9465,7 +9121,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Repayment of term loan (note 11)</t>
+          <t>Proceeds from issuance of revolving loan (note 9)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9474,26 +9130,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F117" s="5" t="n">
-        <v>-46.125</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>-2.5</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="118">
@@ -9509,7 +9165,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of revolving loan (note 11)</t>
+          <t>Repayment of revolving loan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9518,23 +9174,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>30</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>-16.5</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -9555,7 +9209,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Repayment of delayed draw term loan (note 11)</t>
+          <t>Cash settlement for vested RSUs (note 11)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9564,8 +9218,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F119" s="5" t="n">
-        <v>-7.714977</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -9582,10 +9238,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J119" s="5" t="n">
+        <v>-0.119753</v>
       </c>
     </row>
     <row r="120">
@@ -9601,7 +9255,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Repayment of revolving loan (note 11)</t>
+          <t>Repurchase of share capital for cancellation (note 10)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9615,23 +9269,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" s="5" t="n">
-        <v>-19</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>-0.134803</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-2.101298</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>-1.845071</v>
       </c>
     </row>
     <row r="121">
@@ -9647,7 +9297,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital</t>
+          <t>Credit facility financing fees (note 9)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9656,8 +9306,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" s="5" t="n">
-        <v>110.308011</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -9669,10 +9321,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="5" t="n">
+        <v>-1.5039</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9693,35 +9343,39 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of share options</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F122" s="5" t="n">
-        <v>0.15625</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.186477</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="5" t="n">
+        <v>-1.36337</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>-0.901875</v>
       </c>
     </row>
     <row r="123">
@@ -9737,7 +9391,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Repurchase of share capital for cancellation (note 12)</t>
+          <t>Proceeds from sublease</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9751,23 +9405,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>-0.430324</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.599634</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.590893</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>0.461038</v>
       </c>
     </row>
     <row r="124">
@@ -9783,17 +9433,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Credit facility financing fees (note 11)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Net cash provided by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F124" s="5" t="n">
-        <v>-1.274501</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -9805,15 +9461,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="5" t="n">
+        <v>-23.377675</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>3.594339</v>
       </c>
     </row>
     <row r="125">
@@ -9824,44 +9476,38 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lease payments (note 8)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
+          <t>Additions to property and equipment and intangible assets</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F125" s="5" t="n">
-        <v>-0.945076</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>-1.352625</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-2.257811</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>-1.88904</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>-1.318116</v>
       </c>
     </row>
     <row r="126">
@@ -9872,12 +9518,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Proceeds from sublease (note 8)</t>
+          <t>Proceeds from sale of assets</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9886,28 +9532,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="5" t="n">
+        <v>0.020345</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.622604</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.057475</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.191288</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.011747</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>0.164452</v>
       </c>
     </row>
     <row r="127">
@@ -9918,37 +9556,41 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
+          <t>Proceeds from sale of investments</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>-11.194658</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>84.404707</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>-22.473868</v>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="5" t="n">
+        <v>0.01711</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9969,7 +9611,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additions to property and equipment and intangible assets (notes 7 and 9)</t>
+          <t>Acquisitions (note 7 and 8)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -9978,26 +9620,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>-23.688128</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>-9.715075000000001</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="5" t="n">
+        <v>-0.270178</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>-9.737648999999999</v>
       </c>
     </row>
     <row r="129">
@@ -10013,35 +9655,39 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Proceeds from sale of assets</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F129" s="5" t="n">
-        <v>0.020345</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>0.057475</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="5" t="n">
+        <v>-2.130361</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>-10.891313</v>
       </c>
     </row>
     <row r="130">
@@ -10057,37 +9703,35 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Acquisitions (note 4)</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-64.08807400000001</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.251484</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-11.495568</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="5" t="n">
+        <v>-0.734398</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>11.251386</v>
       </c>
     </row>
     <row r="131">
@@ -10103,12 +9747,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Investing activities total</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -10116,26 +9760,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F131" s="5" t="n">
-        <v>-87.75585700000001</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>-9.6576</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>8.766769</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>6.015184</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>5.189315</v>
       </c>
     </row>
     <row r="132">
@@ -10151,39 +9793,29 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Change in restricted cash balances</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>16.251484</v>
+        <v>-0.179743</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>-11.495568</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062913</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.02299</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>-0.003404</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>-0.06725200000000001</v>
       </c>
     </row>
     <row r="133">
@@ -10199,34 +9831,26 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Effect of movement of exchange rates on cash and restricted cash held</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>4.603609</v>
+        <v>-0.181037</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>20.494313</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.294889</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>-0.080641</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>-0.08806700000000001</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -10247,35 +9871,37 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Change in restricted cash balances</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>-0.179743</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>0.062913</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>6.015184</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>5.189315</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>16.373449</v>
       </c>
     </row>
     <row r="135">
@@ -10286,12 +9912,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>functional currency.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Effect of movement of exchange rates on cash and restricted cash held</t>
+          <t>Board of Directors of the Company on March</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10300,26 +9926,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>-0.181037</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>-0.294889</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>3e-06</v>
       </c>
     </row>
     <row r="136">
@@ -10330,17 +9956,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period</t>
+          <t>Depreciation and amortization (notes 6, 7, and 8)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10348,21 +9974,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>20.494313</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>8.766769</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>21.321892</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>17.892421</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -10378,39 +10004,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="n">
-        <v>-1.500701</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>-12.264266</v>
+          <t>Net interest expense (note 16)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>5.087087</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>5.684899</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -10431,19 +10053,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 8, 9, and 10)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>20.19027</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>20.636368</v>
+          <t>Gain on investments</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -10455,10 +10077,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="5" t="n">
+        <v>-0.01711</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -10479,30 +10099,30 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Interest expense (note 20 )</t>
+          <t>Income tax expense (recovery) (note 12)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>5.634257</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>6.073298</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>-2.916993</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>1.760872</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -10523,25 +10143,27 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loss (gain) on sale of assets</t>
+          <t>Adjustment to contingent considerations</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>-0.358807</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0.411209</v>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>-1.051222</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -10567,30 +10189,28 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Loss (gain) on sale of investments</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Income taxes paid</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E141" s="5" t="n">
-        <v>-0.530046</v>
+        <v>-0.39184</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0.000402</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.238942</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-3.86037</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>-0.694349</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>-0.370533</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -10606,35 +10226,35 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) in derivative instruments</t>
+          <t>Proceeds from issuance of revolving loan</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>-0.080957</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.062181</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>41.25</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -10650,37 +10270,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Impairment of Investment (note 11)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Lease payments (note 7)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F143" s="5" t="n">
-        <v>0.25</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H143" s="5" t="n">
+        <v>-1.455419</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>-1.36337</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -10696,30 +10318,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Proceeds from leasehold improvement allowance</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>0.116583</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>-1.830045</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>0.106426</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -10740,39 +10364,33 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 14)</t>
+          <t>Financing activities total</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1.961529</v>
+        <v>-11.194658</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>6.132391</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>84.404707</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-22.473868</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-1.134162</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-23.377675</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -10788,30 +10406,32 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Change in non-cash operating assets and liabilities (note 16)</t>
+          <t>Payment of contingent considerations</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>-4.307957</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>1.564976</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>-15</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -10832,35 +10452,35 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Repayment of initial term loan (note 12)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>-8.25</v>
+          <t>Investing activities total</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-46.125</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-87.75585700000001</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>-9.6576</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>-17.066523</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>-2.130361</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -10876,37 +10496,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of revolving loan (note 12)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Decrease in cash</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F148" s="5" t="n">
-        <v>30</v>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>-2.693934</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>-0.734398</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -10922,30 +10544,32 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Repayment of delayed draw term loan (note 12)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" s="5" t="n">
-        <v>-2.912578</v>
+          <t>Depreciation and amortization (notes 7, 8, and 9)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-7.714977</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.636368</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>38.659197</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>21.321892</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -10966,30 +10590,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Credit facility financing fees (note 12)</t>
+          <t>Net interest expense (note 18)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>-0.109178</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>-1.274501</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>3.094352</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>5.087087</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -11010,34 +10634,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Lease payments (note 9)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
+          <t>Loss (gain) on sale of assets</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" s="5" t="n">
-        <v>-0.822191</v>
+        <v>-0.358807</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>-0.945076</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.411209</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.003198</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>-0.17845</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -11058,27 +10674,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Proceeds from paycheck protection loan (note 12)</t>
+          <t>Impairment of investment (note 10)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" s="5" t="n">
-        <v>0.899289</v>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G152" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11104,30 +10720,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and intangible assets (notes 8, 9, and 10)</t>
+          <t>Income tax recovery (note 14)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="n">
-        <v>-4.716869</v>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>-23.688128</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.830045</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>-2.333054</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>-2.916993</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -11148,30 +10762,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Proceeds from sale of assets</t>
+          <t>Adjustment to contingent considerations (note 4)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>0.442665</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.020345</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.71</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>2.671222</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-1.051222</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -11192,32 +10804,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Proceeds from sale of investments</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" s="5" t="n">
-        <v>0.81925</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation (note 13)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>6.132391</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>9.809234</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>4.517052</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -11238,12 +10850,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Acquisitions (note 4)</t>
+          <t>Change in non-cash operating assets and liabilities (note 15)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -11253,17 +10865,13 @@
         </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>-64.08807400000001</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.564976</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>-1.346439</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>-1.068235</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -11284,30 +10892,30 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and total</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
-        <v>-3.454954</v>
+        <v>-6.629541</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>-87.75585700000001</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.005649</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>-2.307714</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>-4.507773</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -11328,34 +10936,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>-0.546822</v>
+          <t>Repayment of term loan (note 11)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>16.251484</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-46.125</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -11376,34 +10978,30 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Cash, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="n">
-        <v>5.11299</v>
+          <t>Proceeds from issuance of revolving loan (note 11)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>4.603609</v>
+        <v>30</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H159" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -11424,12 +11022,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Restricted cash</t>
+          <t>Repayment of revolving loan (note 11)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11438,18 +11036,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F160" s="5" t="n">
-        <v>-0.179743</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>-12.75</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -11470,25 +11066,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Effect of movement of exchange rates on cash held</t>
+          <t>Proceeds from exercise of share options</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" s="5" t="n">
-        <v>0.037441</v>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>-0.181037</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.15625</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.186477</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -11514,34 +11110,30 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Additions to property and equipment, right-of-use and</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>4.603609</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>20.494313</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repurchase of share capital for cancellation (note 12)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>-0.430324</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>-0.134803</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -11557,33 +11149,37 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Revenue (note 6)</t>
+          <t>Lease payments (note 8)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n">
-        <v>56.923265</v>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>65.761629</v>
+        <v>-0.945076</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>80.488146</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.352625</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>-1.455419</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -11599,33 +11195,35 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wages and consulting</t>
+          <t>Proceeds from sublease (note 8)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>21.46541</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>26.918057</v>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>35.818079</v>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.622604</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.599634</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -11641,17 +11239,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 13)</t>
+          <t>Proceeds from leasehold improvement allowance (note 8)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -11660,16 +11258,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n">
-        <v>6.132391</v>
-      </c>
-      <c r="G165" s="5" t="n">
-        <v>9.809234</v>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>0.106426</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -11685,33 +11285,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Platform and technology</t>
+          <t>Additions to property and equipment and intangible assets (notes 7 and 9)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>6.366223</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>7.177465</v>
+        <v>-23.688128</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>8.816338999999999</v>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.715075000000001</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>-2.257811</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -11727,37 +11327,37 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n">
-        <v>3.356465</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>10.428293</v>
-      </c>
-      <c r="G167" s="5" t="n">
-        <v>7.743383</v>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Payment of contingent considerations (note 4)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>-15</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -11773,22 +11373,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 7, 8, and 9)</t>
+          <t>Increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -11796,16 +11396,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F168" s="5" t="n">
-        <v>20.636368</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>38.659197</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-11.495568</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-2.693934</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -11821,35 +11421,39 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Impairment of investment (note 10)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F169" s="5" t="n">
-        <v>0.25</v>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.494313</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>8.766769</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -11865,35 +11469,39 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Adjustment to contingent considerations (note 4)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F170" s="5" t="n">
-        <v>1.71</v>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>2.671222</v>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.766769</v>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>6.015184</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -11909,32 +11517,30 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="n">
-        <v>53.339897</v>
+          <t>Net interest expense (note 19)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F171" s="5" t="n">
-        <v>73.252574</v>
+        <v>6.073298</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>104.517454</v>
+        <v>3.094352</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -11955,34 +11561,30 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Loss on sale of assets</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>-7.490945</v>
+        <v>0.411209</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>-24.029308</v>
+        <v>0.003198</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -12003,17 +11605,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Loss on sale of assets</t>
+          <t>Loss on sale of investments</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -12023,10 +11625,12 @@
         </is>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0.411209</v>
-      </c>
-      <c r="G173" s="5" t="n">
-        <v>0.003198</v>
+        <v>0.000402</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -12047,34 +11651,30 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net interest expense (note 19)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Unrealized loss in derivative instruments</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>6.073298</v>
+        <v>0.062181</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>3.094352</v>
+        <v>0.018325</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -12095,17 +11695,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Loss on investments</t>
+          <t>Loan forgiveness</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -12115,7 +11715,7 @@
         </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>0.000402</v>
+        <v>-0.899289</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -12141,32 +11741,30 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>0.222082</v>
+          <t>Impairment of Investment (note 10)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" s="5" t="n">
-        <v>0.118457</v>
+        <v>0.25</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>-0.021753</v>
+        <v>1</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -12187,32 +11785,32 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Other expenses total</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="n">
-        <v>4.967486</v>
+          <t>Repayment of delayed draw term loan (note 11)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F177" s="5" t="n">
-        <v>6.603366</v>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>3.075797</v>
+        <v>-7.714977</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -12233,32 +11831,32 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>-1.384118</v>
+          <t>Proceeds from issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-14.094311</v>
-      </c>
-      <c r="G178" s="5" t="n">
-        <v>-27.105105</v>
+        <v>110.308011</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -12279,17 +11877,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Current (note 14)</t>
+          <t>Credit facility financing fees (note 11)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -12299,10 +11897,12 @@
         </is>
       </c>
       <c r="F179" s="5" t="n">
-        <v>0.723939</v>
-      </c>
-      <c r="G179" s="5" t="n">
-        <v>3.093317</v>
+        <v>-1.274501</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -12323,17 +11923,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Deferred (note 14)</t>
+          <t>Acquisitions (note 4)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -12343,10 +11943,12 @@
         </is>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-2.553984</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>-5.426371</v>
+        <v>-64.08807400000001</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -12367,28 +11969,34 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Income taxes (recovery) total</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" s="5" t="n">
-        <v>0.116583</v>
+          <t>Cash and cash equivalents, beginning of the period</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F181" s="5" t="n">
-        <v>-1.830045</v>
+        <v>4.603609</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>-2.333054</v>
+        <v>20.494313</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -12409,32 +12017,34 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Cash and cash equivalents, end of period</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="n">
-        <v>-1.500701</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-12.264266</v>
+        <v>20.494313</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>-24.772051</v>
+        <v>8.766769</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -12455,30 +12065,34 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Items that may be reclassified to net loss</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Foreign currency differences on translation of foreign operations</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>-1.500701</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>-0.144489</v>
-      </c>
-      <c r="G183" s="5" t="n">
-        <v>-0.089472</v>
+        <v>-12.264266</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -12499,30 +12113,34 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Items that may be reclassified to net loss</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation and amortization (notes 8, 9, and 10)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>20.19027</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-12.408755</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>-24.861523</v>
+        <v>20.636368</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -12543,32 +12161,30 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Interest expense (note 20 )</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>5.634257</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>-5.9e-07</v>
-      </c>
-      <c r="G185" s="5" t="n">
-        <v>-1.16e-06</v>
+        <v>6.073298</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -12589,32 +12205,30 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Loss (gain) on sale of investments</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>-0.530046</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>-5.9e-07</v>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>-1.16e-06</v>
+        <v>0.000402</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -12635,25 +12249,27 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 14)</t>
+          <t>Impairment of Investment (note 11)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" s="5" t="n">
-        <v>1.961529</v>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F187" s="5" t="n">
-        <v>6.132391</v>
+        <v>0.25</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -12679,29 +12295,25 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 8, 9, and 10)</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" s="5" t="n">
-        <v>20.19027</v>
+        <v>0.116583</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>20.636368</v>
+        <v>-1.830045</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -12727,27 +12339,29 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Impairment of investment (note 11)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation (note 14)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>1.961529</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>0.25</v>
+        <v>6.132391</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -12773,27 +12387,25 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Adjustment to contingent considerations</t>
+          <t>Change in non-cash operating assets and liabilities (note 16)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E190" s="5" t="n">
+        <v>-4.307957</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>1.71</v>
+        <v>1.564976</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -12819,29 +12431,25 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Operating income (loss)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Repayment of initial term loan (note 12)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" s="5" t="n">
-        <v>3.583368</v>
+        <v>-8.25</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>-7.490945</v>
+        <v>-46.125</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -12867,25 +12475,27 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Loss (gain) on sale of assets</t>
+          <t>Proceeds from issuance of revolving loan (note 12)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" s="5" t="n">
-        <v>-0.358807</v>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.411209</v>
+        <v>30</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -12911,29 +12521,25 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Interest expense (note 20)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Repayment of delayed draw term loan (note 12)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" s="5" t="n">
-        <v>5.634257</v>
+        <v>-2.912578</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>6.073298</v>
+        <v>-7.714977</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -12959,25 +12565,25 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Loss (gain) on investments</t>
+          <t>Credit facility financing fees (note 12)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" s="5" t="n">
-        <v>-0.530046</v>
+        <v>-0.109178</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.000402</v>
+        <v>-1.274501</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -13003,25 +12609,29 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Lease payments (note 9)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E195" s="5" t="n">
-        <v>0.340555</v>
+        <v>-0.822191</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>0.723939</v>
+        <v>-0.945076</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -13047,25 +12657,27 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Proceeds from paycheck protection loan (note 12)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" s="5" t="n">
-        <v>-0.223972</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>-2.553984</v>
+        <v>0.899289</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -13091,25 +12703,25 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Foreign currency differences on translation of foreign</t>
+          <t>Additions to property and equipment, right-of-use and</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Foreign currency differences on translation of foreign operations</t>
+          <t>Additions to property and equipment, right-of-use and intangible assets (notes 8, 9, and 10)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" s="5" t="n">
-        <v>-0.005282</v>
+        <v>-4.716869</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>-0.144489</v>
+        <v>-23.688128</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -13135,42 +12747,2902 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Foreign currency differences on translation of foreign</t>
+          <t>Additions to property and equipment, right-of-use and</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Proceeds from sale of assets</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" s="5" t="n">
+        <v>0.442665</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>0.020345</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of investments</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>0.81925</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Acquisitions (note 4)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>-64.08807400000001</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and total</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>-3.454954</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>-87.75585700000001</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="n">
+        <v>-0.546822</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>16.251484</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Cash, beginning of the period</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>5.11299</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>4.603609</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Restricted cash</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>-0.179743</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Effect of movement of exchange rates on cash held</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.037441</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>-0.181037</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Additions to property and equipment, right-of-use and</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Cash, end of period</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>4.603609</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>20.494313</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Revenue (notes 5 and 18)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>60.899089</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>69.052081</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Wages and consulting</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>21.46541</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>26.918057</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>35.818079</v>
+      </c>
+      <c r="H208" s="5" t="n">
+        <v>28.157502</v>
+      </c>
+      <c r="I208" s="5" t="n">
+        <v>28.095581</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 11)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>4.517052</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>4.091018</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Platform and technology</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>6.366223</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>7.177465</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>8.816338999999999</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>6.941603</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>6.870305</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>3.356465</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>10.428293</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>7.743383</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>4.005025</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>4.780358</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization (notes 6, 7, and 8)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>21.321892</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>17.892421</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Adjustment to contingent considerations</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>-1.051222</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>53.339897</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>73.252574</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>104.517454</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>63.891852</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>61.729683</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Operating income (loss)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>3.583368</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>-7.490945</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>-2.992763</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>7.322398</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>-0.112715</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Gain on sale of assets</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>-0.17845</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>-0.010024</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Net interest and financing expense (note 16)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>5.087087</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>5.684899</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Gain on sale of investments</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>-0.001791</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>-0.01711</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>-0.031661</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>0.032339</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Other expenses (income) total</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>4.875185</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>5.577389</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>-7.867948</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>1.745009</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Current (note 12)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-0.420837</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>1.567662</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Deferred (note 12)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-2.496156</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>0.19321</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery) total</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>-2.333054</v>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>-2.916993</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>1.760872</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>-24.772051</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-4.950955</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>-0.015863</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Items that may be reclassified to net loss</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Foreign currency differences on translation of foreign operations</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>-0.144489</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>-0.089472</v>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>-0.059349</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Items that may be reclassified to net loss</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>-12.408755</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>-24.861523</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>-5.010304</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>-0.015863</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Basic                                             $—           ($0.23)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>-2.3e-07</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Revenue (note 6)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>56.923265</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>65.761629</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>80.488146</v>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>60.899089</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 13)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>6.132391</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>9.809234</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>4.517052</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization (notes 7, 8, and 9)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>20.636368</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>38.659197</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>21.321892</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Impairment of investment (note 10)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Adjustment to contingent considerations (note 4)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>2.671222</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>-1.051222</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Operating loss</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>-7.490945</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>-24.029308</v>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>-2.992763</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Loss (gain) on sale of assets</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" s="5" t="n">
+        <v>-0.358807</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>0.411209</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>0.003198</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>-0.17845</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Net interest expense (note 18)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>3.094352</v>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>5.087087</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Gain on investments</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>-0.001791</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>-0.021753</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>-0.031661</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Other expenses total</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="n">
+        <v>4.967486</v>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>6.603366</v>
+      </c>
+      <c r="G240" s="5" t="n">
+        <v>3.075797</v>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>4.875185</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="n">
+        <v>-1.384118</v>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>-14.094311</v>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>-27.105105</v>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>-7.867948</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Current (note 14)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>3.093317</v>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>-0.420837</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Deferred (note 14)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="n">
+        <v>-5.426371</v>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>-2.496156</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>-5.9e-07</v>
+      </c>
+      <c r="G244" s="5" t="n">
+        <v>-1.16e-06</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>-2.3e-07</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="F245" s="5" t="n">
+        <v>-5.9e-07</v>
+      </c>
+      <c r="G245" s="5" t="n">
+        <v>-1.16e-06</v>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>-2.3e-07</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Loss on sale of assets</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="n">
+        <v>0.411209</v>
+      </c>
+      <c r="G246" s="5" t="n">
+        <v>0.003198</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Net interest expense (note 19)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>6.073298</v>
+      </c>
+      <c r="G247" s="5" t="n">
+        <v>3.094352</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Loss on investments</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.000402</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="n">
+        <v>0.222082</v>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>0.118457</v>
+      </c>
+      <c r="G249" s="5" t="n">
+        <v>-0.021753</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Current (note 14)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>0.723939</v>
+      </c>
+      <c r="G250" s="5" t="n">
+        <v>3.093317</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Deferred (note 14)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>-2.553984</v>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>-5.426371</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) total</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" s="5" t="n">
+        <v>0.116583</v>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>-1.830045</v>
+      </c>
+      <c r="G252" s="5" t="n">
+        <v>-2.333054</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>-1.500701</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>-12.264266</v>
+      </c>
+      <c r="G253" s="5" t="n">
+        <v>-24.772051</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 14)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" s="5" t="n">
+        <v>1.961529</v>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>6.132391</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization (notes 8, 9, and 10)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>20.19027</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>20.636368</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Impairment of investment (note 11)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Interest expense (note 20)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>5.634257</v>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>6.073298</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Loss (gain) on investments</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="5" t="n">
+        <v>-0.530046</v>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>0.000402</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="5" t="n">
+        <v>0.340555</v>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>0.723939</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery)</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
+        <v>-0.223972</v>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>-2.553984</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Foreign currency differences on translation of foreign</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Foreign currency differences on translation of foreign operations</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="5" t="n">
+        <v>-0.005282</v>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>-0.144489</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Foreign currency differences on translation of foreign</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="5" t="n">
         <v>-1.505983</v>
       </c>
-      <c r="F198" s="5" t="n">
+      <c r="F262" s="5" t="n">
         <v>-12.408755</v>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
         <is>
           <t>-</t>
         </is>
